--- a/data/dividends_info_20260618.xlsx
+++ b/data/dividends_info_20260618.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>66.5</v>
+        <v>67.88999938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1353383458646616</v>
+        <v>0.1325673896142689</v>
       </c>
       <c r="J2" t="n">
         <v>270</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.19999694824219</v>
+        <v>65.44999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.073619682153792</v>
+        <v>1.069518766446329</v>
       </c>
       <c r="J3" t="n">
         <v>249</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.319999694824219</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6437768451142812</v>
+        <v>0.6493506654355597</v>
       </c>
       <c r="J4" t="n">
         <v>179</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>66.44000244140625</v>
+        <v>67.88999938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1354605609465042</v>
+        <v>0.1325673896142689</v>
       </c>
       <c r="J6" t="n">
         <v>179</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>158</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.55500030517578</v>
+        <v>21.13999938964844</v>
       </c>
       <c r="I8" t="n">
-        <v>1.252609585605841</v>
+        <v>1.277199658445639</v>
       </c>
       <c r="J8" t="n">
         <v>158</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.909999847412109</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I9" t="n">
-        <v>3.384094842025701</v>
+        <v>3.372681379251118</v>
       </c>
       <c r="J9" t="n">
         <v>151</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.55500030517578</v>
+        <v>21.13999938964844</v>
       </c>
       <c r="I14" t="n">
-        <v>1.252609585605841</v>
+        <v>1.277199658445639</v>
       </c>
       <c r="J14" t="n">
         <v>95</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>66.44000244140625</v>
+        <v>67.88999938964844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1354605609465042</v>
+        <v>0.1325673896142689</v>
       </c>
       <c r="J15" t="n">
         <v>95</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.880000114440918</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="I16" t="n">
-        <v>5.102040717026832</v>
+        <v>5.016722392025687</v>
       </c>
       <c r="J16" t="n">
         <v>88</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.360000133514404</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>4.664178988295694</v>
+        <v>4.681647806299108</v>
       </c>
       <c r="J19" t="n">
         <v>39</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.199999809265137</v>
+        <v>4.179999828338623</v>
       </c>
       <c r="I20" t="n">
-        <v>3.333333484710216</v>
+        <v>3.349282434196755</v>
       </c>
       <c r="J20" t="n">
         <v>32</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.791000366210938</v>
+        <v>9.911999702453613</v>
       </c>
       <c r="I21" t="n">
-        <v>2.655499849609531</v>
+        <v>2.623083210299529</v>
       </c>
       <c r="J21" t="n">
         <v>32</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.23999977111816</v>
+        <v>14.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.213483213791417</v>
+        <v>4.137931034482759</v>
       </c>
       <c r="J22" t="n">
         <v>32</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.625999927520752</v>
+        <v>3.594000101089478</v>
       </c>
       <c r="I23" t="n">
-        <v>6.067291902855144</v>
+        <v>6.121313127768406</v>
       </c>
       <c r="J23" t="n">
         <v>32</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.335000038146973</v>
+        <v>6.409999847412109</v>
       </c>
       <c r="I25" t="n">
-        <v>1.578531955766975</v>
+        <v>1.560062439632861</v>
       </c>
       <c r="J25" t="n">
         <v>32</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.680000066757202</v>
+        <v>2.720000028610229</v>
       </c>
       <c r="I29" t="n">
-        <v>5.597014785954832</v>
+        <v>5.514705824346692</v>
       </c>
       <c r="J29" t="n">
         <v>25</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.79999923706055</v>
+        <v>36.75</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4189944223370775</v>
+        <v>0.4081632653061224</v>
       </c>
       <c r="J32" t="n">
         <v>18</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.5</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="I34" t="n">
-        <v>1.111111111111111</v>
+        <v>1.106194671593815</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.85000038146973</v>
+        <v>29.64999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6532663233098384</v>
+        <v>0.6576728583771428</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.825000047683716</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="I36" t="n">
-        <v>1.808219130836928</v>
+        <v>1.774193534741913</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.510000228881836</v>
+        <v>5.545000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>5.263157676108676</v>
+        <v>5.229936808113163</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.756999969482422</v>
+        <v>3.773999929428101</v>
       </c>
       <c r="I38" t="n">
-        <v>4.258717096078183</v>
+        <v>4.239533730575503</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.634000062942505</v>
+        <v>2.641999959945679</v>
       </c>
       <c r="I39" t="n">
-        <v>5.261958871981446</v>
+        <v>5.246025817610145</v>
       </c>
       <c r="J39" t="n">
         <v>4</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.02000045776367</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I40" t="n">
-        <v>1.211072653702709</v>
+        <v>1.216216234129331</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.15500020980835</v>
+        <v>6.230000019073486</v>
       </c>
       <c r="I41" t="n">
-        <v>2.274573439931032</v>
+        <v>2.247191004356057</v>
       </c>
       <c r="J41" t="n">
         <v>4</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.20000076293945</v>
+        <v>18.10000038146973</v>
       </c>
       <c r="I42" t="n">
-        <v>4.285714106058221</v>
+        <v>4.30939217437002</v>
       </c>
       <c r="J42" t="n">
         <v>4</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>29.06999969482422</v>
+        <v>28.54000091552734</v>
       </c>
       <c r="I43" t="n">
-        <v>2.923976638882932</v>
+        <v>2.978276008174733</v>
       </c>
       <c r="J43" t="n">
         <v>4</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>66.44000244140625</v>
+        <v>67.88999938964844</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1354605609465042</v>
+        <v>0.1325673896142689</v>
       </c>
       <c r="J44" t="n">
         <v>4</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.590000033378601</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6289308044070249</v>
+        <v>0.6451613101701217</v>
       </c>
       <c r="J45" t="n">
         <v>4</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.372000217437744</v>
+        <v>6.414000034332275</v>
       </c>
       <c r="I46" t="n">
-        <v>2.845260417660545</v>
+        <v>2.826629233388741</v>
       </c>
       <c r="J46" t="n">
         <v>4</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.050000190734863</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I47" t="n">
-        <v>2.87292811624668</v>
+        <v>2.863436147407802</v>
       </c>
       <c r="J47" t="n">
         <v>4</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.22000026702881</v>
+        <v>10.38500022888184</v>
       </c>
       <c r="I48" t="n">
-        <v>2.710371749144096</v>
+        <v>2.667308559412761</v>
       </c>
       <c r="J48" t="n">
         <v>4</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.059999942779541</v>
+        <v>1.044999957084656</v>
       </c>
       <c r="I49" t="n">
-        <v>1.273584974410487</v>
+        <v>1.291866081761605</v>
       </c>
       <c r="J49" t="n">
         <v>-3</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.134000062942505</v>
+        <v>3.121999979019165</v>
       </c>
       <c r="I50" t="n">
-        <v>3.509891441952342</v>
+        <v>3.523382470827516</v>
       </c>
       <c r="J50" t="n">
         <v>-3</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.954999923706055</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="I52" t="n">
-        <v>5.414551747241122</v>
+        <v>5.460750728824423</v>
       </c>
       <c r="J52" t="n">
         <v>-10</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>26.89999961853027</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.126394110561131</v>
+        <v>4.051094946911317</v>
       </c>
       <c r="J54" t="n">
         <v>-14</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.9150000214576721</v>
       </c>
       <c r="I55" t="n">
-        <v>3.314917231868003</v>
+        <v>3.278688447701616</v>
       </c>
       <c r="J55" t="n">
         <v>-17</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4709999859333038</v>
+        <v>0.4690000116825104</v>
       </c>
       <c r="I56" t="n">
-        <v>4.883227322061305</v>
+        <v>4.904051050550901</v>
       </c>
       <c r="J56" t="n">
         <v>-17</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.220000267028809</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I58" t="n">
-        <v>2.169197334139026</v>
+        <v>2.132196136032998</v>
       </c>
       <c r="J58" t="n">
         <v>-17</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.410000085830688</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="I59" t="n">
-        <v>7.468879402050181</v>
+        <v>7.531380422563494</v>
       </c>
       <c r="J59" t="n">
         <v>-24</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.53000068664551</v>
+        <v>16.51000022888184</v>
       </c>
       <c r="I61" t="n">
-        <v>1.512401631065712</v>
+        <v>1.514233776706202</v>
       </c>
       <c r="J61" t="n">
         <v>-24</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.46999979019165</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="I63" t="n">
-        <v>3.355704855493265</v>
+        <v>3.340757408605498</v>
       </c>
       <c r="J63" t="n">
         <v>-24</v>
@@ -5136,44 +5136,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>